--- a/aq_files/0092.xlsx
+++ b/aq_files/0092.xlsx
@@ -1,98 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>A teacher wants to find the average marks of students in a class. Which measure of central tendency should be used?</t>
-  </si>
-  <si>
-    <t>A dataset contains extreme values (outliers), and a researcher wants a central value not affected by them. Which measure is most appropriate?</t>
-  </si>
-  <si>
-    <t>In a list of exam scores, the most frequently occurring score is identified. What measure is being used?</t>
-  </si>
-  <si>
-    <t>A company calculates the total salary of employees and divides it by the number of employees. Which measure is this?</t>
-  </si>
-  <si>
-    <t>A dataset has skewed data due to a few very high values. Which measure gives the best central value?</t>
-  </si>
-  <si>
-    <t>A researcher arranges data in ascending order and selects the middle value. What measure is this?</t>
-  </si>
-  <si>
-    <t>A shopkeeper wants to know which product is sold the most frequently. Which measure should be used?</t>
-  </si>
-  <si>
-    <t>A dataset has no repeated values. Which measure may not be meaningful in this case?</t>
-  </si>
-  <si>
-    <t>A teacher calculates the sum of marks and divides by the number of students. What measure is this?</t>
-  </si>
-  <si>
-    <t>A researcher uses the middle value of ordered data to represent the dataset. Which measure is this?</t>
-  </si>
-  <si>
-    <t>In a salary dataset where most employees earn similar wages but a few earn very high salaries, which measure is most reliable?</t>
-  </si>
-  <si>
-    <t>A dataset contains values: 2, 3, 3, 5, 7. Which measure identifies 3 as the central value based on frequency?</t>
-  </si>
-  <si>
-    <t>A researcher wants a quick measure of the central value that uses all observations. Which measure should be used?</t>
-  </si>
-  <si>
-    <t>A dataset is symmetric with no outliers. Which measure is most appropriate to represent the center?</t>
-  </si>
-  <si>
-    <t>A statistician uses a measure that may not exist if no values repeat. Which measure is this?</t>
-  </si>
-  <si>
-    <t>A researcher is analyzing household income and wants to avoid distortion from very high incomes. Which measure should be used?</t>
-  </si>
-  <si>
-    <t>A dataset has multiple values occurring with the same highest frequency. What is the situation called?</t>
-  </si>
-  <si>
-    <t>A teacher wants to know the middle score after arranging marks in order. Which measure is used?</t>
-  </si>
-  <si>
-    <t>A business analyzes the most common shoe size sold in a store. Which measure is applied?</t>
-  </si>
-  <si>
-    <t>A researcher calculates the central value by summing all values and dividing by the count. Which measure is this?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,1033 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B61"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Row_ID,Order_Reference,Order_Date_Text,Order_DateTime,Product_Hierarchy,Product_Name,Category,SubCategory,Sales_Value, Qty , Discount% ,Profit_Value,Full_Customer_Name,Email_Address,Phone_Number,Address_Full,City_State_Zip,Country,Region_Code,Order_Status,Return_Flag,Customer_Notes,Last_Updated</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1,ORD-1001,2024-01-05,2024-01-05 14:30:00,Electronics|Computers|Laptops,MacBook Pro,Electronics,Computers,1299.99,1,5%,389.99,"Smith, John",john.smith@email.com,555-0101,"123 Main Street",Chicago IL 60601,USA,NW,Active,N,"Premium customer - prefers express shipping",2024-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2,ORD-1002,2024-01-05,2024-01-05 14:35:00,Electronics|Accessories|Mice,Magic Mouse,Electronics,Accessories,79.99,3,10%,23.99,"Smith, John",john.smith@email.com,555-0101,"123 Main Street",Chicago IL 60601,USA,NW,Active,N,"",2024-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>3,ORD-1003,2024-01-06,2024-01-06 09:15:00,Clothing|Mens|Denim,Designer Jeans,Clothing,Mens,89.99,2,0%,26.99,"Lee, Sarah",sarah.lee@email.com,555-0102,"456 Oak Avenue",Houston TX 77001,USA,SW,Active,N,"First time customer - send welcome email",2024-01-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4,ORD-1004,2024-01-06,2024-01-06 10:45:00,Electronics|Monitors|4K,27-inch Monitor,Electronics,Monitors,299.99,1,15%,89.99,"Brown, Michael",michael.b@email.com,555-0103,"789 Pine Street",Austin TX 78701,USA,SW,Active,N,"",2024-01-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>5,ORD-1005,2024-01-07,2024-01-07 11:20:00,Furniture|Chairs|Executive,Executive Chair,Furniture,Chairs,399.99,2,5%,119.99,"Davis, Emily",emily.d@email.com,555-0104,"321 Elm Street",New York NY 10001,USA,NE,Active,N,"VIP customer - high lifetime value",2024-01-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6,ORD-1006,2024-01-07,2024-01-07 13:00:00,Electronics|Keyboards|Mechanical,Mechanical Keyboard,Electronics,Keyboards,89.99,2,10%,26.99,"Wilson, David",david.w@email.com,555-0105,"654 Maple Avenue",Buffalo NY 14201,USA,NE,Active,N,"",2024-01-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>7,ORD-1007,2024-01-08,2024-01-08 08:45:00,Clothing|Womens|Outerwear,Leather Jacket,Clothing,Womens,199.99,1,20%,59.99,"Anderson, Lisa",lisa.a@email.com,555-0106,"987 Cedar Lane",Los Angeles CA 90001,USA,WC,Active,N,"",2024-01-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8,ORD-1008,2024-01-08,2024-01-08 09:30:00,Electronics|Tablets|iPad,iPad,Electronics,Tablets,499.99,1,5%,149.99,"Taylor, Robert",robert.t@email.com,555-0107,"147 Birch Street",San Francisco CA 94101,USA,WC,Active,N,"",2024-01-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>9,ORD-1009,2024-01-09,2024-01-09 10:15:00,Furniture|Lighting|Floor Lamps,Floor Lamp,Furniture,Lighting,79.99,2,0%,23.99,"Martinez, Jennifer",jennifer.m@email.com,555-0108,"258 Spruce Avenue",Chicago IL 60602,USA,NW,Active,N,"",2024-01-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>10,ORD-1010,2024-01-09,2024-01-09 14:20:00,Clothing|Mens|Footwear,Running Shoes,Clothing,Mens,69.99,1,10%,20.99,"Brown, William",william.b@email.com,555-0109,"369 Walnut Street",Detroit MI 48201,USA,NW,Returned,Y,"Size issue - customer requested return",2024-01-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>11,ORD-1011,2024-01-10,2024-01-10 11:00:00,Electronics|Computers|Gaming,Gaming Laptop,Electronics,Computers,1299.99,1,15%,389.99,"Davis, Patricia",patricia.d@email.com,555-0110,"741 Cherry Lane",Dallas TX 75201,USA,SW,Active,N,"",2024-01-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12,ORD-1012,2024-01-10,2024-01-10 15:30:00,Electronics|Audio|Headphones,Headphones,Electronics,Audio,149.99,2,5%,44.99,"Miller, Michael",michael.m@email.com,555-0111,"852 Dogwood Drive",Philadelphia PA 19101,USA,NE,Active,N,"",2024-01-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>13,ORD-1013,2024-01-11,2024-01-11 09:45:00,Clothing|Womens|Outerwear,Wool Coat,Clothing,Womens,189.99,1,20%,56.99,"Wilson, Linda",linda.w@email.com,555-0112,"963 Magnolia Road",San Diego CA 92101,USA,WC,Active,N,"",2024-01-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>14,ORD-1014,2024-01-11,2024-01-11 12:15:00,Furniture|Storage|Bookcases,Bookshelf,Furniture,Storage,159.99,1,10%,47.99,"Moore, Richard",richard.m@email.com,555-0113,"159 Cypress Court",Columbus OH 43201,USA,NW,Active,N,"",2024-01-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>15,ORD-1015,2024-01-12,2024-01-12 10:00:00,Electronics|Phones|Smartphones,Smartphone,Electronics,Phones,699.99,2,5%,209.99,"Taylor, Susan",susan.t@email.com,555-0114,"753 Palm Avenue",Miami FL 33101,USA,SW,Active,N,"",2024-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>16,ORD-1016,2024-01-12,2024-01-12 13:45:00,Clothing|Mens|Shirts,Dress Shirt,Clothing,Mens,59.99,3,0%,17.99,"Anderson, Thomas",thomas.a@email.com,555-0115,"951 Holly Street",New York NY 10002,USA,NE,Active,N,"",2024-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>17,ORD-1017,2024-01-13,2024-01-13 08:30:00,Electronics|Storage|SSD,External SSD,Electronics,Storage,99.99,1,10%,29.99,"Thomas, Jessica",jessica.t@email.com,555-0116,"852 Fir Lane",Portland OR 97201,USA,WC,Active,N,"",2024-01-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>18,ORD-1018,2024-01-13,2024-01-13 16:20:00,Clothing|Womens|Tops,Hoodie,Clothing,Womens,49.99,2,5%,14.99,"Jackson, Charles",charles.j@email.com,555-0117,"753 Spruce Avenue",Chicago IL 60603,USA,NW,Returned,Y,"Wrong size - exchange requested",2024-01-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>19,ORD-1019,2024-01-14,2024-01-14 11:30:00,Furniture|Desks|Gaming,Gaming Desk,Furniture,Desks,349.99,1,15%,104.99,"White, Sarah",sarah.w@email.com,555-0118,"951 Willow Drive",Austin TX 78702,USA,SW,Active,N,"",2024-01-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>20,ORD-1020,2024-01-14,2024-01-14 14:15:00,Electronics|Accessories|Webcams,Webcam,Electronics,Accessories,79.99,2,10%,23.99,"Harris, Daniel",daniel.h@email.com,555-0119,"357 Ash Street",Boston MA 02101,USA,NE,Active,N,"",2024-01-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>21,ORD-1021,2024-02-01,2024-02-01 09:00:00,Electronics|Docks|Docking,Docking Station,Electronics,Docks,129.99,1,0%,38.99,"Clark, Matthew",matthew.c@email.com,555-0120,"159 Beech Court",Seattle WA 98101,USA,WC,Active,N,"",2024-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>22,ORD-1022,2024-02-01,2024-02-01 10:45:00,Clothing|Mens|Outerwear,Winter Parka,Clothing,Mens,179.99,1,5%,53.99,"Lewis, Amanda",amanda.l@email.com,555-0121,"753 Poplar Avenue",Minneapolis MN 55401,USA,NW,Active,N,"",2024-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>23,ORD-1023,2024-02-02,2024-02-02 13:30:00,Furniture|Desks|Office,Office Desk,Furniture,Desks,449.99,1,10%,134.99,"Walker, James",james.w@email.com,555-0122,"951 Cedar Street",Orlando FL 32801,USA,SW,Active,N,"",2024-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>24,ORD-1024,2024-02-02,2024-02-02 15:20:00,Electronics|Cables|USB,USB-C Hub,Electronics,Cables,39.99,3,0%,11.99,"Hall, Betty",betty.h@email.com,555-0123,"357 Maple Lane",Newark NJ 07101,USA,NE,Active,N,"",2024-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>25,ORD-1025,2024-02-03,2024-02-03 08:15:00,Clothing|Mens|Blazers,Casual Blazer,Clothing,Mens,149.99,1,15%,44.99,"Young, Kevin",kevin.y@email.com,555-0124,"753 Elm Drive",Los Angeles CA 90002,USA,WC,Active,N,"",2024-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>26,ORD-1026,2024-02-03,2024-02-03 11:45:00,Electronics|Accessories|Mice,Gaming Mouse,Electronics,Accessories,59.99,2,10%,17.99,"Allen, Nancy",nancy.a@email.com,555-0125,"159 Oak Court",Indianapolis IN 46201,USA,NW,Returned,Y,"Defective product - replacement needed",2024-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>27,ORD-1027,2024-02-04,2024-02-04 09:30:00,Electronics|Printers|Laser,Laser Printer,Electronics,Printers,199.99,1,5%,59.99,"King, Edward",edward.k@email.com,555-0126,"357 Pine Avenue",Atlanta GA 30301,USA,SW,Active,N,"",2024-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>28,ORD-1028,2024-02-04,2024-02-04 14:00:00,Furniture|Chairs|Lounge,Lounge Chair,Furniture,Chairs,279.99,1,20%,83.99,"Wright, Donna",donna.w@email.com,555-0127,"951 Birch Street",Richmond VA 23201,USA,NE,Active,N,"",2024-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>29,ORD-1029,2024-02-05,2024-02-05 10:15:00,Electronics|Batteries|Power Banks,Power Bank,Electronics,Batteries,49.99,4,0%,14.99,"Lopez, George",george.l@email.com,555-0128,"753 Cedar Avenue",Phoenix AZ 85001,USA,WC,Active,N,"",2024-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>30,ORD-1030,2024-02-05,2024-02-05 12:30:00,Clothing|Accessories|Scarves,Wool Scarf,Clothing,Accessories,24.99,5,10%,7.49,"Hill, Sandra",sandra.h@email.com,555-0129,"159 Walnut Lane",Milwaukee WI 53201,USA,NW,Active,N,"",2024-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>31,ORD-1031,2024-02-06,2024-02-06 13:45:00,Electronics|Audio|Headphones,Gaming Headset,Electronics,Audio,119.99,1,5%,35.99,"Scott, Brian",brian.s@email.com,555-0130,"357 Dogwood Drive",Houston TX 77002,USA,SW,Active,N,"",2024-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>32,ORD-1032,2024-02-06,2024-02-06 15:30:00,Furniture|Storage|Nightstands,Night Stand,Furniture,Storage,69.99,2,10%,20.99,"Adams, Carolyn",carolyn.a@email.com,555-0131,"753 Magnolia Road",Rochester NY 14601,USA,NE,Active,N,"",2024-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>33,ORD-1033,2024-02-07,2024-02-07 09:20:00,Clothing|Mens|Footwear,Athletic Shoes,Clothing,Mens,109.99,1,15%,32.99,"Baker, Frank",frank.b@email.com,555-0132,"159 Cypress Court",San Jose CA 95101,USA,WC,Active,N,"",2024-02-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>34,ORD-1034,2024-02-07,2024-02-07 11:00:00,Electronics|Wearables|Watches,Smart Watch,Electronics,Wearables,199.99,1,5%,59.99,"Gonzalez, Ruth",ruth.g@email.com,555-0133,"357 Palm Avenue",St Louis MO 63101,USA,NW,Active,N,"",2024-02-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>35,ORD-1035,2024-02-08,2024-02-08 14:15:00,Electronics|Audio|Speakers,Bluetooth Speaker,Electronics,Audio,79.99,2,10%,23.99,"Nelson, Peter",peter.n@email.com,555-0134,"951 Holly Street",Tampa FL 33601,USA,SW,Active,N,"",2024-02-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>36,ORD-1036,2024-02-08,2024-02-08 16:45:00,Clothing|Womens|Sweaters,Cashmere Sweater,Clothing,Womens,99.99,1,0%,29.99,"Carter, Kimberly",kimberly.c@email.com,555-0135,"753 Fir Lane",Pittsburgh PA 15201,USA,NE,Returned,Y,"Quality issue - fabric defect",2024-02-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>37,ORD-1037,2024-02-09,2024-02-09 10:30:00,Furniture|Storage|Bookcases,Bookshelf,Furniture,Storage,129.99,1,5%,38.99,"Mitchell, Steven",steven.m@email.com,555-0136,"159 Spruce Avenue",Eugene OR 97401,USA,WC,Active,N,"",2024-02-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>38,ORD-1038,2024-02-09,2024-02-09 12:00:00,Electronics|Networking|Routers,Mesh Router,Electronics,Networking,99.99,1,10%,29.99,"Perez, Laura",laura.p@email.com,555-0137,"357 Willow Drive",Des Moines IA 50301,USA,NW,Active,N,"",2024-02-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>39,ORD-1039,2024-02-10,2024-02-10 09:45:00,Clothing|Mens|Polos,Golf Polo,Clothing,Mens,44.99,3,15%,13.49,"Roberts, Paul",paul.r@email.com,555-0138,"753 Ash Street",San Antonio TX 78201,USA,SW,Active,N,"",2024-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>40,ORD-1040,2024-02-10,2024-02-10 13:15:00,Electronics|Components|Graphics,Graphics Card,Electronics,Components,499.99,1,20%,149.99,"Turner, Mary",mary.t@email.com,555-0139,"159 Beech Court",Spokane WA 99201,USA,WC,Active,N,"",2024-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>41,ORD-1041,2024-03-01,2024-03-01 10:00:00,Electronics|Computers|Desktops,Desktop PC,Electronics,Computers,999.99,1,5%,299.99,"Phillips, Daniel",daniel.p@email.com,555-0140,"357 Poplar Avenue",Chicago IL 60604,USA,NW,Active,N,"",2024-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>42,ORD-1042,2024-03-01,2024-03-01 11:30:00,Clothing|Womens|Bottoms,Yoga Pants,Clothing,Womens,49.99,2,0%,14.99,"Campbell, Lisa",lisa.c@email.com,555-0141,"753 Cedar Street",Austin TX 78703,USA,SW,Active,N,"",2024-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>43,ORD-1043,2024-03-02,2024-03-02 14:45:00,Furniture|Tables|Coffee,Coffee Table,Furniture,Tables,249.99,1,10%,74.99,"Parker, Ronald",ronald.p@email.com,555-0142,"951 Maple Lane",New York NY 10003,USA,NE,Active,N,"",2024-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>44,ORD-1044,2024-03-02,2024-03-02 16:20:00,Electronics|Smart Home|Speakers,Smart Speaker,Electronics,Smart Home,89.99,2,0%,26.99,"Evans, Deborah",deborah.e@email.com,555-0143,"357 Elm Drive",Los Angeles CA 90003,USA,WC,Active,N,"",2024-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>45,ORD-1045,2024-03-03,2024-03-03 08:30:00,Clothing|Accessories|Hats,Baseball Cap,Clothing,Accessories,19.99,4,5%,5.99,"Edwards, Joseph",joseph.e@email.com,555-0144,"159 Oak Court",Detroit MI 48202,USA,NW,Active,N,"",2024-03-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>46,ORD-1046,2024-03-03,2024-03-03 12:15:00,Electronics|Drones|Quadcopter,Quadcopter,Electronics,Drones,349.99,1,10%,104.99,"Collins, Barbara",barbara.c@email.com,555-0145,"753 Pine Avenue",Miami FL 33102,USA,SW,Active,N,"",2024-03-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>47,ORD-1047,2024-03-04,2024-03-04 09:45:00,Furniture|Decor|Mirrors,Wall Mirror,Furniture,Decor,59.99,2,0%,17.99,"Stewart, Mark",mark.s@email.com,555-0146,"951 Birch Street",Philadelphia PA 19102,USA,NE,Active,N,"",2024-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>48,ORD-1048,2024-03-04,2024-03-04 13:30:00,Clothing|Mens|Shirts,Flannel Shirt,Clothing,Mens,49.99,2,10%,14.99,"Morris, Carol",carol.m@email.com,555-0147,"357 Cedar Avenue",Portland OR 97202,USA,WC,Active,N,"",2024-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>49,ORD-1049,2024-03-05,2024-03-05 10:30:00,Electronics|Streaming|Sticks,Streaming Stick,Electronics,Streaming,29.99,3,5%,8.99,"Rogers, Raymond",raymond.r@email.com,555-0148,"753 Walnut Lane",Columbus OH 43202,USA,NW,Returned,Y,"Not working properly - defective",2024-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>50,ORD-1050,2024-03-05,2024-03-05 14:00:00,Clothing|Womens|Bottoms,Leggings,Clothing,Womens,29.99,4,0%,8.99,"Reed, Anna",anna.r@email.com,555-0149,"159 Dogwood Drive",Atlanta GA 30302,USA,SW,Active,N,"",2024-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3051,2024-02-11,West,California,Los Angeles,Electronics,Monitors,Ultrawide Monitor,549.99,2,549.98,0.15,22.00,Corporate</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3052,2024-02-11,North,Illinois,Chicago,Clothing,Mens,Denim Jacket,89.99,5,224.98,0.10,12.00,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3053,2024-02-12,South,Texas,Houston,Furniture,Chairs,Gaming Chair,299.99,2,299.98,0.05,22.00,Corporate</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3054,2024-02-12,East,New York,Buffalo,Electronics,Audio,Portable Speaker,79.99,4,159.98,0.00,10.00,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3055,2024-02-13,West,Washington,Seattle,Clothing,Womens,Rain Jacket,129.99,3,194.98,0.15,12.00,Home Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3056,2024-02-13,North,Minnesota,Minneapolis,Electronics,Storage,Portable SSD,89.99,5,224.98,0.10,8.50,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3057,2024-02-14,South,Florida,Orlando,Electronics,Phones,Smartphone Case,29.99,15,224.85,0.00,8.50,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3058,2024-02-14,East,Massachusetts,Boston,Furniture,Lighting,Desk Lamp,59.99,6,179.97,0.05,12.00,Corporate</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3059,2024-02-15,West,California,San Diego,Clothing,Accessories,Leather Belt,39.99,8,159.96,0.10,8.50,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3060,2024-02-15,North,Ohio,Columbus,Electronics,Accessories,Phone Stand,19.99,12,119.94,0.00,8.50,Consumer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Load the dataset into Power Query Editor. Identify all columns that have incorrect data types. List them with their current and correct data types.</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Convert 'Order_Date_Text' from Text to Date type. Handle any conversion errors. How many rows have invalid dates?</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Convert 'Sales_Value' from Text to Decimal Number. Remove any non-numeric characters like spaces before conversion.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Convert ' Qty ' column (note the spaces in column name) from Text to Whole Number. Also clean the column name to remove spaces.</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Convert 'Discount%' from Text to Percentage. Remove the % symbol and convert to proper percentage format.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Product_Hierarchy' column by delimiter '|' into three columns: 'Product_Level1', 'Product_Level2', 'Product_Level3'.</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Full_Customer_Name' column into 'First_Name' and 'Last_Name' using comma delimiter. Handle the 'Last, First' format.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'City_State_Zip' column into three separate columns: 'City', 'State', 'Zip' using space delimiter.</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Merge the 'City', 'State', 'Zip' columns back into a single 'Full_Location' column with comma and space separators.</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Address_Full' column into 'Street_Address' and 'Address_Line2' using a delimiter (look for 'Street', 'Avenue', etc.).</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Order_Size' that categorizes Quantity: &gt;3 = 'Bulk Order', 2-3 = 'Standard Order', 1 = 'Single Item'.</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Sales_Tier' based on Sales_Value: &gt;1000 = 'Premium', 500-1000 = 'High', 200-500 = 'Medium', &lt;200 = 'Low'.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Profit_Status' based on Profit_Value: &gt;100 = 'Highly Profitable', &gt;0 = 'Profitable', &lt;=0 = 'Loss'.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Create a Column from Examples to extract the domain from Email_Address (text after '@'). Type examples like 'email.com' for the first few rows.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Extract the first 3 characters from 'Order_Reference' into a new column named 'Order_Prefix'.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Extract the last 4 characters from 'Order_Reference' into a new column named 'Order_Number'.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Trim whitespace from all text columns and standardize 'Region_Code' to uppercase.</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Replace all blank/null values in 'Customer_Notes' column with 'No notes'.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Filter rows where 'Order_Status' is 'Active'. How many rows remain? Then create a separate query for 'Returned' orders.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Data Cleansing and Manipulation_</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Group rows by 'Category' and calculate Total Sales, Total Profit, Average Discount, and Order Count. What are the results for Electronics?</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>